--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMTechniqueImagerie vers le profil CDA FRCDADICOMTechniqueImagerie, puis vers le profil FHIR FRProcedureImagingDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMProcedure vers le profil CDA FRCDADICOMTechniqueImagerie, puis vers le profil FHIR FRProcedureImagingDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-technique-imagerie</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-technique-imagerie</t>
   </si>
   <si>
-    <t>FRLMTechniqueImagerie</t>
+    <t>FRLMProcedure</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,49 +118,67 @@
     <t>FRCDADICOMTechniqueImagerie</t>
   </si>
   <si>
-    <t>FRLMTechniqueImagerie.identifiant</t>
+    <t>FRLMProcedure.header.identifier</t>
   </si>
   <si>
     <t>FRCDADICOMTechniqueImagerie.id</t>
   </si>
   <si>
-    <t>FRLMTechniqueImagerie.codeActe</t>
+    <t>FRLMProcedure.code</t>
   </si>
   <si>
     <t>FRCDADICOMTechniqueImagerie.code</t>
   </si>
   <si>
-    <t>FRLMTechniqueImagerie.description</t>
-  </si>
-  <si>
-    <t>FRCDADICOMTechniqueImagerie.text</t>
-  </si>
-  <si>
-    <t>FRLMTechniqueImagerie.date</t>
+    <t>FRLMProcedure.header.status</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.procedureDate[x]</t>
   </si>
   <si>
     <t>FRCDADICOMTechniqueImagerie.effectiveTime</t>
   </si>
   <si>
-    <t>FRLMTechniqueImagerie.modaliteAcquisition</t>
-  </si>
-  <si>
-    <t>FRCDADICOMTechniqueImagerie.methodCode</t>
-  </si>
-  <si>
-    <t>FRLMTechniqueImagerie.lateralite</t>
+    <t>FRLMProcedure.procedureDateDateTime</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.effectiveTime.low</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.procedureDatePeriod</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.effectiveTime.high</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.priority</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.priorityCode</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.bodySite</t>
   </si>
   <si>
     <t>FRCDADICOMTechniqueImagerie.targetSiteCode</t>
   </si>
   <si>
-    <t>FRLMTechniqueImagerie.lateralite.precisionTopographique</t>
+    <t>FRLMProcedure.bodySite:FRLMBodyStructure.locationQualifier</t>
   </si>
   <si>
     <t>FRCDADICOMTechniqueImagerie.targetSiteCode.qualifier</t>
   </si>
   <si>
-    <t>FRLMTechniqueImagerie.participant</t>
+    <t>FRLMProcedure.approachSiteCode</t>
+  </si>
+  <si>
+    <t>FRCDADICOMTechniqueImagerie.approachSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.header.participant[x]</t>
   </si>
   <si>
     <t>FRCDADICOMTechniqueImagerie.participant</t>
@@ -178,13 +196,82 @@
     <t>FRProcedureImagingDocument.code</t>
   </si>
   <si>
+    <t>FRProcedureImagingDocument.status</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.performed[x]</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.extension:priority</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.bodySite</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.extension:approachBodySite</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.difficulty</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.extension:difficulte</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.reason[x]</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.reasonReference</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.outcome</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.outcome</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.complication</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.complication</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.deviceUsed</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.usedReference</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.focalDevice</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.focalDevice.manipulated</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.note</t>
+  </si>
+  <si>
     <t>FRProcedureImagingDocument.note</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.performed[x]</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.bodySite</t>
+    <t>FRLMProcedure.header.performer[x]</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.performer:Intervenant.actor</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.header.author[x]</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.recorder</t>
+  </si>
+  <si>
+    <t>FRLMProcedure.header.informant</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.asserter</t>
+  </si>
+  <si>
+    <t>FRProcedureImagingDocument.extension:participant</t>
   </si>
 </sst>
 </file>
@@ -436,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -589,6 +676,45 @@
         <v>49</v>
       </c>
       <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -597,7 +723,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -619,7 +745,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -628,7 +754,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -636,103 +762,250 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>63</v>
+      </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>64</v>
+      </c>
       <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E21" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedure|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-technique-imagerie</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-technique-imagerie|0.1.0</t>
   </si>
   <si>
     <t>FRLMProcedure</t>
@@ -184,7 +184,7 @@
     <t>FRCDADICOMTechniqueImagerie.participant</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-procedure-imaging-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-imaging-document|0.1.0</t>
   </si>
   <si>
     <t>FRProcedureImagingDocument</t>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRImagingProcedureLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +106,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedure|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMProcedure|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,73 +121,61 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Procedure</t>
+  </si>
+  <si>
     <t>FRCDADICOMTechniqueImagerie</t>
   </si>
   <si>
     <t>FRLMProcedure.header.identifier</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.id</t>
+    <t>Procedure.id</t>
   </si>
   <si>
     <t>FRLMProcedure.code</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.code</t>
+    <t>Procedure.code</t>
   </si>
   <si>
     <t>FRLMProcedure.header.status</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.statusCode</t>
+    <t>Procedure.statusCode</t>
   </si>
   <si>
     <t>FRLMProcedure.procedureDate[x]</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDateDateTime</t>
-  </si>
-  <si>
-    <t>FRCDADICOMTechniqueImagerie.effectiveTime.low</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.procedureDatePeriod</t>
-  </si>
-  <si>
-    <t>FRCDADICOMTechniqueImagerie.effectiveTime.high</t>
+    <t>Procedure.effectiveTime</t>
   </si>
   <si>
     <t>FRLMProcedure.priority</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.priorityCode</t>
+    <t>Procedure.priorityCode</t>
   </si>
   <si>
     <t>FRLMProcedure.bodySite</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.targetSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMProcedure.bodySite:FRLMBodyStructure.locationQualifier</t>
-  </si>
-  <si>
-    <t>FRCDADICOMTechniqueImagerie.targetSiteCode.qualifier</t>
+    <t>Procedure.targetSiteCode</t>
+  </si>
+  <si>
+    <t>Procedure.targetSiteCode.qualifier</t>
   </si>
   <si>
     <t>FRLMProcedure.approachSiteCode</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.approachSiteCode</t>
+    <t>Procedure.approachSiteCode</t>
   </si>
   <si>
     <t>FRLMProcedure.header.participant[x]</t>
   </si>
   <si>
-    <t>FRCDADICOMTechniqueImagerie.participant</t>
+    <t>Procedure.participant</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-imaging-document|0.1.0</t>
@@ -190,88 +184,85 @@
     <t>FRProcedureImagingDocument</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.code</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.status</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.performed[x]</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.extension:priority</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.bodySite</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.extension:approachBodySite</t>
+    <t>Procedure.identifier</t>
+  </si>
+  <si>
+    <t>Procedure.status</t>
+  </si>
+  <si>
+    <t>Procedure.performed[x]</t>
+  </si>
+  <si>
+    <t>Procedure.extension:priority</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite</t>
+  </si>
+  <si>
+    <t>Procedure.extension:approachBodySite</t>
   </si>
   <si>
     <t>FRLMProcedure.difficulty</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.extension:difficulte</t>
+    <t>Procedure.extension:difficulte</t>
   </si>
   <si>
     <t>FRLMProcedure.reason[x]</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.reasonReference</t>
+    <t>Procedure.reasonReference</t>
   </si>
   <si>
     <t>FRLMProcedure.outcome</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.outcome</t>
+    <t>Procedure.outcome</t>
   </si>
   <si>
     <t>FRLMProcedure.complication</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.complication</t>
+    <t>Procedure.complication</t>
   </si>
   <si>
     <t>FRLMProcedure.deviceUsed</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.usedReference</t>
+    <t>Procedure.usedReference</t>
   </si>
   <si>
     <t>FRLMProcedure.focalDevice</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.focalDevice.manipulated</t>
+    <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
     <t>FRLMProcedure.note</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.note</t>
+    <t>Procedure.note</t>
   </si>
   <si>
     <t>FRLMProcedure.header.performer[x]</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.performer:Intervenant.actor</t>
+    <t>Procedure.performer:intervenant.actor</t>
   </si>
   <si>
     <t>FRLMProcedure.header.author[x]</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.recorder</t>
+    <t>Procedure.recorder</t>
   </si>
   <si>
     <t>FRLMProcedure.header.informant</t>
   </si>
   <si>
-    <t>FRProcedureImagingDocument.asserter</t>
-  </si>
-  <si>
-    <t>FRProcedureImagingDocument.extension:participant</t>
+    <t>Procedure.asserter</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant</t>
   </si>
 </sst>
 </file>
@@ -440,79 +431,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -523,198 +518,174 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="E14" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -728,282 +699,284 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
     </row>

--- a/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
+++ b/main/ig/FRImagingProcedureLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
